--- a/datasets/AML1 colony size in glucose.xlsx
+++ b/datasets/AML1 colony size in glucose.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\OneDrive - Wageningen University &amp; Research\UCI_projects\Project_8 (Reviews)\Family\Pere\doctorado\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0809170-964F-48DF-868A-E431CCBED891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC2D92-AFD1-4A0C-8AA4-43AD434F8CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B9045DA2-5F59-4FD1-A553-B2CC705338E4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="38">
   <si>
     <t>WTa</t>
   </si>
@@ -136,6 +136,21 @@
   </si>
   <si>
     <t>light</t>
+  </si>
+  <si>
+    <t>Plots</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -3867,14 +3882,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493727F2-72BD-4FB8-AD65-B7C035C4CD94}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -3887,8 +3902,11 @@
       <c r="D1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -3901,8 +3919,11 @@
       <c r="D2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3915,8 +3936,11 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3929,8 +3953,11 @@
       <c r="D4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3943,8 +3970,11 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3957,8 +3987,11 @@
       <c r="D6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3971,8 +4004,11 @@
       <c r="D7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3985,8 +4021,11 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3999,8 +4038,11 @@
       <c r="D9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -4013,8 +4055,11 @@
       <c r="D10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4027,8 +4072,11 @@
       <c r="D11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -4041,8 +4089,11 @@
       <c r="D12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -4055,8 +4106,11 @@
       <c r="D13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -4069,8 +4123,11 @@
       <c r="D14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -4083,8 +4140,11 @@
       <c r="D15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -4097,8 +4157,11 @@
       <c r="D16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -4111,8 +4174,11 @@
       <c r="D17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -4125,8 +4191,11 @@
       <c r="D18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -4139,8 +4208,11 @@
       <c r="D19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -4153,8 +4225,11 @@
       <c r="D20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -4167,8 +4242,11 @@
       <c r="D21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -4181,8 +4259,11 @@
       <c r="D22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -4195,8 +4276,11 @@
       <c r="D23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4209,8 +4293,11 @@
       <c r="D24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -4223,8 +4310,11 @@
       <c r="D25" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
@@ -4237,8 +4327,11 @@
       <c r="D26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
@@ -4251,8 +4344,11 @@
       <c r="D27" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
@@ -4265,8 +4361,11 @@
       <c r="D28" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
@@ -4279,8 +4378,11 @@
       <c r="D29" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>12</v>
       </c>
@@ -4293,8 +4395,11 @@
       <c r="D30" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
@@ -4307,8 +4412,11 @@
       <c r="D31" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>14</v>
       </c>
@@ -4321,8 +4429,11 @@
       <c r="D32" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>15</v>
       </c>
@@ -4334,6 +4445,9 @@
       </c>
       <c r="D33" t="s">
         <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
